--- a/dist/Foxy_Fight_Sheet_Template.xlsx
+++ b/dist/Foxy_Fight_Sheet_Template.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statuses" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opponents" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CutIns" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fighters" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,7 +47,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +79,16 @@
         <fgColor rgb="00E6D3EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6D6B8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8E2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -90,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -121,6 +133,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -488,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -752,7 +770,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Put an image filename (e.g. ps_jab.png, served from the game's art/ folder) or a full https:// image link in the art column. Blank = generated art-deco art.</t>
+          <t>Put an image filename (e.g. ps_jab.png, served from the game's art/ folder) or a full https:// image link in the art column. Blank = generated art-deco art. A value with a / in it (art/cutins/...) is used as a path from the game folder.</t>
         </is>
       </c>
     </row>
@@ -760,6 +778,65 @@
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>End-of-fight images: Opponents tab win_art (shown when you beat her) and loss_art (shown when she beats you). Config default_win_art / default_loss_art cover any blanks. Wide 16:9 images work best.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Cut-in art (CutIns and Fighters tabs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>You don't need to edit anything here to add art. Every picture already has its path in CutIns. Drop the files into the game's art/cutins/&lt;fighter&gt;/ folders with the names listed in each folder's README.txt and upload. A picture that isn't there yet is skipped and the nearest one is used instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>If your own Google Sheet has no CutIns or Fighters tab, the game uses its built-in copy. Add these tabs to your sheet only if you want to change paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>CutIns: one row per fighter + move. fighter = a style id, an opponent id or a Fighters id. move = a card id, a tag (Opener, Light, Heavy, Finisher, Guard, Wild), Knockdown, Victory, or blank for any move. profile_0..2 / pov_0..2 = image paths or https:// links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>The numbers: on card and tag rows, knockdowns that fighter has taken (0 fresh, 1 worn, 2 battered). Knockdown row: 0 = first knockdown, 1 = second, 2 = T.K.O. Victory row: the knockdowns the winner took.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Your fighter is always shown in profile, the opponent in POV. Ladder opponents only have pov paths. Upgrades (+) use their base card's row; Finishers and Elites have their own rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Fighters: custom looks a player can pick. style = the style she dresses. outfit_of = the Fighters id this is an evolved outfit of (blank for her base look). Her rows use tags, not cards. Run npm run art-list after adding one to get her paths and folder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Art problems never block the sheet: a typo shows as a warning and that picture falls back.</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3384,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -7841,7 +7918,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -9489,4 +9566,4524 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I139"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>fighter</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>profile_0</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>profile_1</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>profile_2</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>pov_0</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>pov_1</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>pov_2</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>petal_storm</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Opener</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/opener_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/opener_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/opener_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/opener_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/opener_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/opener_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>petal_storm</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/light_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/light_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/light_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/light_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/light_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/light_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>petal_storm</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/heavy_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/heavy_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/heavy_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/heavy_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/heavy_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/heavy_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>petal_storm</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/guard_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/guard_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/guard_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/guard_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/guard_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/guard_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>petal_storm</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Wild</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/wild_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/wild_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/wild_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/wild_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/wild_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/wild_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>petal_storm</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>ps_flurry</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/encore_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/encore_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/encore_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/encore_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/encore_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/encore_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>petal_storm</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Knockdown</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/knockdown_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/knockdown_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/knockdown_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/knockdown_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/knockdown_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/knockdown_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>petal_storm</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/victory_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/victory_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/victory_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/victory_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/victory_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/victory_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>sakura_tempest</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Opener</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/opener_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/opener_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/opener_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/opener_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/opener_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/opener_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>sakura_tempest</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/light_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/light_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/light_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/light_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/light_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/light_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>sakura_tempest</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/heavy_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/heavy_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/heavy_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/heavy_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/heavy_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/heavy_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>sakura_tempest</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/guard_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/guard_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/guard_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/guard_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/guard_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/guard_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>sakura_tempest</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Wild</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/wild_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/wild_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/wild_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/wild_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/wild_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/wild_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>sakura_tempest</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>ps_flurry</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/encore_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/encore_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/encore_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/encore_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/encore_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/encore_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>sakura_tempest</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>ps_bloom</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/curtain_call_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/curtain_call_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/curtain_call_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/curtain_call_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/curtain_call_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/curtain_call_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>sakura_tempest</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>ps_hurricane</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/standing_ovation_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/standing_ovation_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/standing_ovation_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/standing_ovation_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/standing_ovation_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/standing_ovation_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>sakura_tempest</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Knockdown</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/knockdown_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/knockdown_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/knockdown_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/knockdown_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/knockdown_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/knockdown_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>sakura_tempest</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/victory_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/victory_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/victory_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/victory_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/victory_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/victory_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>stone_lotus</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Opener</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/opener_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/opener_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/opener_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/opener_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/opener_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/opener_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>stone_lotus</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/light_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/light_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/light_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/light_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/light_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/light_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>stone_lotus</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/heavy_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/heavy_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/heavy_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/heavy_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/heavy_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/heavy_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>stone_lotus</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/guard_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/guard_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/guard_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/guard_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/guard_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/guard_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>stone_lotus</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Wild</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/wild_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/wild_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/wild_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/wild_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/wild_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/wild_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>stone_lotus</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>sl_throw</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/last_call_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/last_call_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/last_call_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/last_call_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/last_call_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/last_call_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>stone_lotus</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Knockdown</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/knockdown_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/knockdown_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/knockdown_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/knockdown_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/knockdown_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/knockdown_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>stone_lotus</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/victory_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/victory_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/victory_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/victory_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/victory_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/victory_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>jade_colossus</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Opener</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/opener_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/opener_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/opener_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/opener_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/opener_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/opener_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>jade_colossus</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/light_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/light_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/light_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/light_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/light_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/light_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>jade_colossus</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/heavy_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/heavy_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/heavy_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/heavy_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/heavy_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/heavy_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>jade_colossus</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/guard_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/guard_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/guard_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/guard_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/guard_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/guard_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>jade_colossus</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Wild</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/wild_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/wild_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/wild_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/wild_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/wild_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/wild_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>jade_colossus</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>sl_throw</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/last_call_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/last_call_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/last_call_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/last_call_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/last_call_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/last_call_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>jade_colossus</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>sl_avalanche</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/ten_count_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/ten_count_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/ten_count_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/ten_count_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/ten_count_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/ten_count_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>jade_colossus</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>sl_monolith</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/bouncers_guard_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/bouncers_guard_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/bouncers_guard_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/bouncers_guard_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/bouncers_guard_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/bouncers_guard_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>jade_colossus</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Knockdown</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/knockdown_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/knockdown_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/knockdown_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/knockdown_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/knockdown_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/knockdown_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>jade_colossus</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/victory_profile_0.png</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/victory_profile_1.png</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/victory_profile_2.png</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/victory_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/victory_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/victory_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>opp_mochi</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Opener</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr"/>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/opener_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/opener_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/opener_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>opp_mochi</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/light_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/light_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/light_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>opp_mochi</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr"/>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/heavy_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/heavy_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/heavy_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>opp_mochi</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/guard_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/guard_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/guard_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>opp_mochi</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>ps_flurry</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr"/>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/encore_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/encore_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/encore_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>opp_mochi</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Knockdown</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr"/>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/knockdown_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/knockdown_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/knockdown_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>opp_mochi</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/victory_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/victory_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/lola-lux/victory_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>opp_juniper</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Opener</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/opener_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/opener_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/opener_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>opp_juniper</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr"/>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/light_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/light_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/light_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>opp_juniper</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr"/>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/heavy_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/heavy_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/heavy_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>opp_juniper</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr"/>
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/guard_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/guard_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/guard_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>opp_juniper</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>sl_throw</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr"/>
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/last_call_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/last_call_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/last_call_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>opp_juniper</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Knockdown</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/knockdown_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/knockdown_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/knockdown_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>opp_juniper</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/victory_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/victory_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/dolores-dee-maddox/victory_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>opp_kiko</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Opener</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr"/>
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/opener_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/opener_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/opener_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>opp_kiko</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr"/>
+      <c r="D53" s="5" t="inlineStr"/>
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/light_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/light_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/light_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>opp_kiko</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr"/>
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/heavy_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/heavy_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/heavy_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>opp_kiko</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/guard_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/guard_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/guard_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>opp_kiko</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>ps_flurry</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr"/>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/encore_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/encore_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/encore_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>opp_kiko</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Knockdown</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr"/>
+      <c r="D57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/knockdown_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/knockdown_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/knockdown_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>opp_kiko</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr"/>
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/victory_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/victory_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/vicki-high-score-starr/victory_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>opp_marlowe</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Opener</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr"/>
+      <c r="D59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/opener_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/opener_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/opener_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>opp_marlowe</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr"/>
+      <c r="D60" s="5" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/light_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/light_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/light_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>opp_marlowe</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr"/>
+      <c r="D61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/heavy_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/heavy_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/heavy_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>opp_marlowe</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr"/>
+      <c r="D62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr"/>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/guard_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/guard_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/guard_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>opp_marlowe</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>sl_throw</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr"/>
+      <c r="D63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr"/>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/last_call_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/last_call_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/last_call_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>opp_marlowe</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Knockdown</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr"/>
+      <c r="D64" s="5" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/knockdown_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/knockdown_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/knockdown_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>opp_marlowe</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr"/>
+      <c r="D65" s="5" t="inlineStr"/>
+      <c r="E65" s="5" t="inlineStr"/>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/victory_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/victory_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/ingrid-kessler/victory_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>opp_sora</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Opener</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr"/>
+      <c r="D66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/opener_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/opener_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/opener_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>opp_sora</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr"/>
+      <c r="D67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr"/>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/light_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/light_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/light_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>opp_sora</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr"/>
+      <c r="D68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr"/>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/heavy_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/heavy_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/heavy_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>opp_sora</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr"/>
+      <c r="D69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr"/>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/guard_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/guard_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/guard_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>opp_sora</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>ps_flurry</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr"/>
+      <c r="D70" s="5" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr"/>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/encore_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/encore_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/encore_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>opp_sora</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Knockdown</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr"/>
+      <c r="D71" s="5" t="inlineStr"/>
+      <c r="E71" s="5" t="inlineStr"/>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/knockdown_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/knockdown_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/knockdown_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>opp_sora</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr"/>
+      <c r="D72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/victory_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/victory_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/scarlett-delacroix/victory_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>opp_jade</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Opener</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr"/>
+      <c r="D73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr"/>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/opener_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/opener_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/opener_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>opp_jade</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr"/>
+      <c r="D74" s="5" t="inlineStr"/>
+      <c r="E74" s="5" t="inlineStr"/>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/light_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/light_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/light_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>opp_jade</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr"/>
+      <c r="D75" s="5" t="inlineStr"/>
+      <c r="E75" s="5" t="inlineStr"/>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/heavy_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/heavy_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/heavy_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>opp_jade</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr"/>
+      <c r="D76" s="5" t="inlineStr"/>
+      <c r="E76" s="5" t="inlineStr"/>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/guard_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/guard_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/guard_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>opp_jade</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>sl_throw</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr"/>
+      <c r="D77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/last_call_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/last_call_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/last_call_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>opp_jade</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>sl_monolith</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr"/>
+      <c r="D78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr"/>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/bouncers_guard_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/bouncers_guard_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/bouncers_guard_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>opp_jade</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Knockdown</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr"/>
+      <c r="D79" s="5" t="inlineStr"/>
+      <c r="E79" s="5" t="inlineStr"/>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/knockdown_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/knockdown_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/knockdown_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>opp_jade</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr"/>
+      <c r="D80" s="5" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/victory_pov_0.png</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/victory_pov_1.png</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/victory_pov_2.png</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n"/>
+      <c r="B81" s="7" t="n"/>
+      <c r="C81" s="7" t="n"/>
+      <c r="D81" s="7" t="n"/>
+      <c r="E81" s="7" t="n"/>
+      <c r="F81" s="7" t="n"/>
+      <c r="G81" s="7" t="n"/>
+      <c r="H81" s="7" t="n"/>
+      <c r="I81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n"/>
+      <c r="B82" s="7" t="n"/>
+      <c r="C82" s="7" t="n"/>
+      <c r="D82" s="7" t="n"/>
+      <c r="E82" s="7" t="n"/>
+      <c r="F82" s="7" t="n"/>
+      <c r="G82" s="7" t="n"/>
+      <c r="H82" s="7" t="n"/>
+      <c r="I82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n"/>
+      <c r="B83" s="7" t="n"/>
+      <c r="C83" s="7" t="n"/>
+      <c r="D83" s="7" t="n"/>
+      <c r="E83" s="7" t="n"/>
+      <c r="F83" s="7" t="n"/>
+      <c r="G83" s="7" t="n"/>
+      <c r="H83" s="7" t="n"/>
+      <c r="I83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n"/>
+      <c r="B84" s="7" t="n"/>
+      <c r="C84" s="7" t="n"/>
+      <c r="D84" s="7" t="n"/>
+      <c r="E84" s="7" t="n"/>
+      <c r="F84" s="7" t="n"/>
+      <c r="G84" s="7" t="n"/>
+      <c r="H84" s="7" t="n"/>
+      <c r="I84" s="7" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n"/>
+      <c r="B85" s="7" t="n"/>
+      <c r="C85" s="7" t="n"/>
+      <c r="D85" s="7" t="n"/>
+      <c r="E85" s="7" t="n"/>
+      <c r="F85" s="7" t="n"/>
+      <c r="G85" s="7" t="n"/>
+      <c r="H85" s="7" t="n"/>
+      <c r="I85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n"/>
+      <c r="B86" s="7" t="n"/>
+      <c r="C86" s="7" t="n"/>
+      <c r="D86" s="7" t="n"/>
+      <c r="E86" s="7" t="n"/>
+      <c r="F86" s="7" t="n"/>
+      <c r="G86" s="7" t="n"/>
+      <c r="H86" s="7" t="n"/>
+      <c r="I86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n"/>
+      <c r="B87" s="7" t="n"/>
+      <c r="C87" s="7" t="n"/>
+      <c r="D87" s="7" t="n"/>
+      <c r="E87" s="7" t="n"/>
+      <c r="F87" s="7" t="n"/>
+      <c r="G87" s="7" t="n"/>
+      <c r="H87" s="7" t="n"/>
+      <c r="I87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n"/>
+      <c r="B88" s="7" t="n"/>
+      <c r="C88" s="7" t="n"/>
+      <c r="D88" s="7" t="n"/>
+      <c r="E88" s="7" t="n"/>
+      <c r="F88" s="7" t="n"/>
+      <c r="G88" s="7" t="n"/>
+      <c r="H88" s="7" t="n"/>
+      <c r="I88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n"/>
+      <c r="B89" s="7" t="n"/>
+      <c r="C89" s="7" t="n"/>
+      <c r="D89" s="7" t="n"/>
+      <c r="E89" s="7" t="n"/>
+      <c r="F89" s="7" t="n"/>
+      <c r="G89" s="7" t="n"/>
+      <c r="H89" s="7" t="n"/>
+      <c r="I89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n"/>
+      <c r="B90" s="7" t="n"/>
+      <c r="C90" s="7" t="n"/>
+      <c r="D90" s="7" t="n"/>
+      <c r="E90" s="7" t="n"/>
+      <c r="F90" s="7" t="n"/>
+      <c r="G90" s="7" t="n"/>
+      <c r="H90" s="7" t="n"/>
+      <c r="I90" s="7" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n"/>
+      <c r="B91" s="7" t="n"/>
+      <c r="C91" s="7" t="n"/>
+      <c r="D91" s="7" t="n"/>
+      <c r="E91" s="7" t="n"/>
+      <c r="F91" s="7" t="n"/>
+      <c r="G91" s="7" t="n"/>
+      <c r="H91" s="7" t="n"/>
+      <c r="I91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n"/>
+      <c r="B92" s="7" t="n"/>
+      <c r="C92" s="7" t="n"/>
+      <c r="D92" s="7" t="n"/>
+      <c r="E92" s="7" t="n"/>
+      <c r="F92" s="7" t="n"/>
+      <c r="G92" s="7" t="n"/>
+      <c r="H92" s="7" t="n"/>
+      <c r="I92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n"/>
+      <c r="B93" s="7" t="n"/>
+      <c r="C93" s="7" t="n"/>
+      <c r="D93" s="7" t="n"/>
+      <c r="E93" s="7" t="n"/>
+      <c r="F93" s="7" t="n"/>
+      <c r="G93" s="7" t="n"/>
+      <c r="H93" s="7" t="n"/>
+      <c r="I93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n"/>
+      <c r="B94" s="7" t="n"/>
+      <c r="C94" s="7" t="n"/>
+      <c r="D94" s="7" t="n"/>
+      <c r="E94" s="7" t="n"/>
+      <c r="F94" s="7" t="n"/>
+      <c r="G94" s="7" t="n"/>
+      <c r="H94" s="7" t="n"/>
+      <c r="I94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n"/>
+      <c r="B95" s="7" t="n"/>
+      <c r="C95" s="7" t="n"/>
+      <c r="D95" s="7" t="n"/>
+      <c r="E95" s="7" t="n"/>
+      <c r="F95" s="7" t="n"/>
+      <c r="G95" s="7" t="n"/>
+      <c r="H95" s="7" t="n"/>
+      <c r="I95" s="7" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n"/>
+      <c r="B96" s="7" t="n"/>
+      <c r="C96" s="7" t="n"/>
+      <c r="D96" s="7" t="n"/>
+      <c r="E96" s="7" t="n"/>
+      <c r="F96" s="7" t="n"/>
+      <c r="G96" s="7" t="n"/>
+      <c r="H96" s="7" t="n"/>
+      <c r="I96" s="7" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n"/>
+      <c r="B97" s="7" t="n"/>
+      <c r="C97" s="7" t="n"/>
+      <c r="D97" s="7" t="n"/>
+      <c r="E97" s="7" t="n"/>
+      <c r="F97" s="7" t="n"/>
+      <c r="G97" s="7" t="n"/>
+      <c r="H97" s="7" t="n"/>
+      <c r="I97" s="7" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n"/>
+      <c r="B98" s="7" t="n"/>
+      <c r="C98" s="7" t="n"/>
+      <c r="D98" s="7" t="n"/>
+      <c r="E98" s="7" t="n"/>
+      <c r="F98" s="7" t="n"/>
+      <c r="G98" s="7" t="n"/>
+      <c r="H98" s="7" t="n"/>
+      <c r="I98" s="7" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n"/>
+      <c r="B99" s="7" t="n"/>
+      <c r="C99" s="7" t="n"/>
+      <c r="D99" s="7" t="n"/>
+      <c r="E99" s="7" t="n"/>
+      <c r="F99" s="7" t="n"/>
+      <c r="G99" s="7" t="n"/>
+      <c r="H99" s="7" t="n"/>
+      <c r="I99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n"/>
+      <c r="B100" s="7" t="n"/>
+      <c r="C100" s="7" t="n"/>
+      <c r="D100" s="7" t="n"/>
+      <c r="E100" s="7" t="n"/>
+      <c r="F100" s="7" t="n"/>
+      <c r="G100" s="7" t="n"/>
+      <c r="H100" s="7" t="n"/>
+      <c r="I100" s="7" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="n"/>
+      <c r="B101" s="7" t="n"/>
+      <c r="C101" s="7" t="n"/>
+      <c r="D101" s="7" t="n"/>
+      <c r="E101" s="7" t="n"/>
+      <c r="F101" s="7" t="n"/>
+      <c r="G101" s="7" t="n"/>
+      <c r="H101" s="7" t="n"/>
+      <c r="I101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="n"/>
+      <c r="B102" s="7" t="n"/>
+      <c r="C102" s="7" t="n"/>
+      <c r="D102" s="7" t="n"/>
+      <c r="E102" s="7" t="n"/>
+      <c r="F102" s="7" t="n"/>
+      <c r="G102" s="7" t="n"/>
+      <c r="H102" s="7" t="n"/>
+      <c r="I102" s="7" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="n"/>
+      <c r="B103" s="7" t="n"/>
+      <c r="C103" s="7" t="n"/>
+      <c r="D103" s="7" t="n"/>
+      <c r="E103" s="7" t="n"/>
+      <c r="F103" s="7" t="n"/>
+      <c r="G103" s="7" t="n"/>
+      <c r="H103" s="7" t="n"/>
+      <c r="I103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="n"/>
+      <c r="B104" s="7" t="n"/>
+      <c r="C104" s="7" t="n"/>
+      <c r="D104" s="7" t="n"/>
+      <c r="E104" s="7" t="n"/>
+      <c r="F104" s="7" t="n"/>
+      <c r="G104" s="7" t="n"/>
+      <c r="H104" s="7" t="n"/>
+      <c r="I104" s="7" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="n"/>
+      <c r="B105" s="7" t="n"/>
+      <c r="C105" s="7" t="n"/>
+      <c r="D105" s="7" t="n"/>
+      <c r="E105" s="7" t="n"/>
+      <c r="F105" s="7" t="n"/>
+      <c r="G105" s="7" t="n"/>
+      <c r="H105" s="7" t="n"/>
+      <c r="I105" s="7" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="n"/>
+      <c r="B106" s="7" t="n"/>
+      <c r="C106" s="7" t="n"/>
+      <c r="D106" s="7" t="n"/>
+      <c r="E106" s="7" t="n"/>
+      <c r="F106" s="7" t="n"/>
+      <c r="G106" s="7" t="n"/>
+      <c r="H106" s="7" t="n"/>
+      <c r="I106" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="n"/>
+      <c r="B107" s="7" t="n"/>
+      <c r="C107" s="7" t="n"/>
+      <c r="D107" s="7" t="n"/>
+      <c r="E107" s="7" t="n"/>
+      <c r="F107" s="7" t="n"/>
+      <c r="G107" s="7" t="n"/>
+      <c r="H107" s="7" t="n"/>
+      <c r="I107" s="7" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="n"/>
+      <c r="B108" s="7" t="n"/>
+      <c r="C108" s="7" t="n"/>
+      <c r="D108" s="7" t="n"/>
+      <c r="E108" s="7" t="n"/>
+      <c r="F108" s="7" t="n"/>
+      <c r="G108" s="7" t="n"/>
+      <c r="H108" s="7" t="n"/>
+      <c r="I108" s="7" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="n"/>
+      <c r="B109" s="7" t="n"/>
+      <c r="C109" s="7" t="n"/>
+      <c r="D109" s="7" t="n"/>
+      <c r="E109" s="7" t="n"/>
+      <c r="F109" s="7" t="n"/>
+      <c r="G109" s="7" t="n"/>
+      <c r="H109" s="7" t="n"/>
+      <c r="I109" s="7" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="n"/>
+      <c r="B110" s="7" t="n"/>
+      <c r="C110" s="7" t="n"/>
+      <c r="D110" s="7" t="n"/>
+      <c r="E110" s="7" t="n"/>
+      <c r="F110" s="7" t="n"/>
+      <c r="G110" s="7" t="n"/>
+      <c r="H110" s="7" t="n"/>
+      <c r="I110" s="7" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="n"/>
+      <c r="B111" s="7" t="n"/>
+      <c r="C111" s="7" t="n"/>
+      <c r="D111" s="7" t="n"/>
+      <c r="E111" s="7" t="n"/>
+      <c r="F111" s="7" t="n"/>
+      <c r="G111" s="7" t="n"/>
+      <c r="H111" s="7" t="n"/>
+      <c r="I111" s="7" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n"/>
+      <c r="B112" s="7" t="n"/>
+      <c r="C112" s="7" t="n"/>
+      <c r="D112" s="7" t="n"/>
+      <c r="E112" s="7" t="n"/>
+      <c r="F112" s="7" t="n"/>
+      <c r="G112" s="7" t="n"/>
+      <c r="H112" s="7" t="n"/>
+      <c r="I112" s="7" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="n"/>
+      <c r="B113" s="7" t="n"/>
+      <c r="C113" s="7" t="n"/>
+      <c r="D113" s="7" t="n"/>
+      <c r="E113" s="7" t="n"/>
+      <c r="F113" s="7" t="n"/>
+      <c r="G113" s="7" t="n"/>
+      <c r="H113" s="7" t="n"/>
+      <c r="I113" s="7" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n"/>
+      <c r="B114" s="7" t="n"/>
+      <c r="C114" s="7" t="n"/>
+      <c r="D114" s="7" t="n"/>
+      <c r="E114" s="7" t="n"/>
+      <c r="F114" s="7" t="n"/>
+      <c r="G114" s="7" t="n"/>
+      <c r="H114" s="7" t="n"/>
+      <c r="I114" s="7" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="n"/>
+      <c r="B115" s="7" t="n"/>
+      <c r="C115" s="7" t="n"/>
+      <c r="D115" s="7" t="n"/>
+      <c r="E115" s="7" t="n"/>
+      <c r="F115" s="7" t="n"/>
+      <c r="G115" s="7" t="n"/>
+      <c r="H115" s="7" t="n"/>
+      <c r="I115" s="7" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n"/>
+      <c r="B116" s="7" t="n"/>
+      <c r="C116" s="7" t="n"/>
+      <c r="D116" s="7" t="n"/>
+      <c r="E116" s="7" t="n"/>
+      <c r="F116" s="7" t="n"/>
+      <c r="G116" s="7" t="n"/>
+      <c r="H116" s="7" t="n"/>
+      <c r="I116" s="7" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="n"/>
+      <c r="B117" s="7" t="n"/>
+      <c r="C117" s="7" t="n"/>
+      <c r="D117" s="7" t="n"/>
+      <c r="E117" s="7" t="n"/>
+      <c r="F117" s="7" t="n"/>
+      <c r="G117" s="7" t="n"/>
+      <c r="H117" s="7" t="n"/>
+      <c r="I117" s="7" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n"/>
+      <c r="B118" s="7" t="n"/>
+      <c r="C118" s="7" t="n"/>
+      <c r="D118" s="7" t="n"/>
+      <c r="E118" s="7" t="n"/>
+      <c r="F118" s="7" t="n"/>
+      <c r="G118" s="7" t="n"/>
+      <c r="H118" s="7" t="n"/>
+      <c r="I118" s="7" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="n"/>
+      <c r="B119" s="7" t="n"/>
+      <c r="C119" s="7" t="n"/>
+      <c r="D119" s="7" t="n"/>
+      <c r="E119" s="7" t="n"/>
+      <c r="F119" s="7" t="n"/>
+      <c r="G119" s="7" t="n"/>
+      <c r="H119" s="7" t="n"/>
+      <c r="I119" s="7" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n"/>
+      <c r="B120" s="7" t="n"/>
+      <c r="C120" s="7" t="n"/>
+      <c r="D120" s="7" t="n"/>
+      <c r="E120" s="7" t="n"/>
+      <c r="F120" s="7" t="n"/>
+      <c r="G120" s="7" t="n"/>
+      <c r="H120" s="7" t="n"/>
+      <c r="I120" s="7" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="n"/>
+      <c r="B121" s="7" t="n"/>
+      <c r="C121" s="7" t="n"/>
+      <c r="D121" s="7" t="n"/>
+      <c r="E121" s="7" t="n"/>
+      <c r="F121" s="7" t="n"/>
+      <c r="G121" s="7" t="n"/>
+      <c r="H121" s="7" t="n"/>
+      <c r="I121" s="7" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="n"/>
+      <c r="B122" s="7" t="n"/>
+      <c r="C122" s="7" t="n"/>
+      <c r="D122" s="7" t="n"/>
+      <c r="E122" s="7" t="n"/>
+      <c r="F122" s="7" t="n"/>
+      <c r="G122" s="7" t="n"/>
+      <c r="H122" s="7" t="n"/>
+      <c r="I122" s="7" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="n"/>
+      <c r="B123" s="7" t="n"/>
+      <c r="C123" s="7" t="n"/>
+      <c r="D123" s="7" t="n"/>
+      <c r="E123" s="7" t="n"/>
+      <c r="F123" s="7" t="n"/>
+      <c r="G123" s="7" t="n"/>
+      <c r="H123" s="7" t="n"/>
+      <c r="I123" s="7" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="n"/>
+      <c r="B124" s="7" t="n"/>
+      <c r="C124" s="7" t="n"/>
+      <c r="D124" s="7" t="n"/>
+      <c r="E124" s="7" t="n"/>
+      <c r="F124" s="7" t="n"/>
+      <c r="G124" s="7" t="n"/>
+      <c r="H124" s="7" t="n"/>
+      <c r="I124" s="7" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="n"/>
+      <c r="B125" s="7" t="n"/>
+      <c r="C125" s="7" t="n"/>
+      <c r="D125" s="7" t="n"/>
+      <c r="E125" s="7" t="n"/>
+      <c r="F125" s="7" t="n"/>
+      <c r="G125" s="7" t="n"/>
+      <c r="H125" s="7" t="n"/>
+      <c r="I125" s="7" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="n"/>
+      <c r="B126" s="7" t="n"/>
+      <c r="C126" s="7" t="n"/>
+      <c r="D126" s="7" t="n"/>
+      <c r="E126" s="7" t="n"/>
+      <c r="F126" s="7" t="n"/>
+      <c r="G126" s="7" t="n"/>
+      <c r="H126" s="7" t="n"/>
+      <c r="I126" s="7" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="n"/>
+      <c r="B127" s="7" t="n"/>
+      <c r="C127" s="7" t="n"/>
+      <c r="D127" s="7" t="n"/>
+      <c r="E127" s="7" t="n"/>
+      <c r="F127" s="7" t="n"/>
+      <c r="G127" s="7" t="n"/>
+      <c r="H127" s="7" t="n"/>
+      <c r="I127" s="7" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="n"/>
+      <c r="B128" s="7" t="n"/>
+      <c r="C128" s="7" t="n"/>
+      <c r="D128" s="7" t="n"/>
+      <c r="E128" s="7" t="n"/>
+      <c r="F128" s="7" t="n"/>
+      <c r="G128" s="7" t="n"/>
+      <c r="H128" s="7" t="n"/>
+      <c r="I128" s="7" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="n"/>
+      <c r="B129" s="7" t="n"/>
+      <c r="C129" s="7" t="n"/>
+      <c r="D129" s="7" t="n"/>
+      <c r="E129" s="7" t="n"/>
+      <c r="F129" s="7" t="n"/>
+      <c r="G129" s="7" t="n"/>
+      <c r="H129" s="7" t="n"/>
+      <c r="I129" s="7" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="n"/>
+      <c r="B130" s="7" t="n"/>
+      <c r="C130" s="7" t="n"/>
+      <c r="D130" s="7" t="n"/>
+      <c r="E130" s="7" t="n"/>
+      <c r="F130" s="7" t="n"/>
+      <c r="G130" s="7" t="n"/>
+      <c r="H130" s="7" t="n"/>
+      <c r="I130" s="7" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="n"/>
+      <c r="B131" s="7" t="n"/>
+      <c r="C131" s="7" t="n"/>
+      <c r="D131" s="7" t="n"/>
+      <c r="E131" s="7" t="n"/>
+      <c r="F131" s="7" t="n"/>
+      <c r="G131" s="7" t="n"/>
+      <c r="H131" s="7" t="n"/>
+      <c r="I131" s="7" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="n"/>
+      <c r="B132" s="7" t="n"/>
+      <c r="C132" s="7" t="n"/>
+      <c r="D132" s="7" t="n"/>
+      <c r="E132" s="7" t="n"/>
+      <c r="F132" s="7" t="n"/>
+      <c r="G132" s="7" t="n"/>
+      <c r="H132" s="7" t="n"/>
+      <c r="I132" s="7" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="n"/>
+      <c r="B133" s="7" t="n"/>
+      <c r="C133" s="7" t="n"/>
+      <c r="D133" s="7" t="n"/>
+      <c r="E133" s="7" t="n"/>
+      <c r="F133" s="7" t="n"/>
+      <c r="G133" s="7" t="n"/>
+      <c r="H133" s="7" t="n"/>
+      <c r="I133" s="7" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="n"/>
+      <c r="B134" s="7" t="n"/>
+      <c r="C134" s="7" t="n"/>
+      <c r="D134" s="7" t="n"/>
+      <c r="E134" s="7" t="n"/>
+      <c r="F134" s="7" t="n"/>
+      <c r="G134" s="7" t="n"/>
+      <c r="H134" s="7" t="n"/>
+      <c r="I134" s="7" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="n"/>
+      <c r="B135" s="7" t="n"/>
+      <c r="C135" s="7" t="n"/>
+      <c r="D135" s="7" t="n"/>
+      <c r="E135" s="7" t="n"/>
+      <c r="F135" s="7" t="n"/>
+      <c r="G135" s="7" t="n"/>
+      <c r="H135" s="7" t="n"/>
+      <c r="I135" s="7" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="n"/>
+      <c r="B136" s="7" t="n"/>
+      <c r="C136" s="7" t="n"/>
+      <c r="D136" s="7" t="n"/>
+      <c r="E136" s="7" t="n"/>
+      <c r="F136" s="7" t="n"/>
+      <c r="G136" s="7" t="n"/>
+      <c r="H136" s="7" t="n"/>
+      <c r="I136" s="7" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="n"/>
+      <c r="B137" s="7" t="n"/>
+      <c r="C137" s="7" t="n"/>
+      <c r="D137" s="7" t="n"/>
+      <c r="E137" s="7" t="n"/>
+      <c r="F137" s="7" t="n"/>
+      <c r="G137" s="7" t="n"/>
+      <c r="H137" s="7" t="n"/>
+      <c r="I137" s="7" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="n"/>
+      <c r="B138" s="7" t="n"/>
+      <c r="C138" s="7" t="n"/>
+      <c r="D138" s="7" t="n"/>
+      <c r="E138" s="7" t="n"/>
+      <c r="F138" s="7" t="n"/>
+      <c r="G138" s="7" t="n"/>
+      <c r="H138" s="7" t="n"/>
+      <c r="I138" s="7" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="n"/>
+      <c r="B139" s="7" t="n"/>
+      <c r="C139" s="7" t="n"/>
+      <c r="D139" s="7" t="n"/>
+      <c r="E139" s="7" t="n"/>
+      <c r="F139" s="7" t="n"/>
+      <c r="G139" s="7" t="n"/>
+      <c r="H139" s="7" t="n"/>
+      <c r="I139" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>outfit_of</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>art</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t># Example (rows starting with # are ignored): a custom fighter for the Cherry Bomb line with an evolved outfit.</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr"/>
+      <c r="C2" s="5" t="inlineStr"/>
+      <c r="D2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t># roxy</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Roxy Vale</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>petal_storm</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>art/fighters/roxy.webp</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t># roxy_main</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Roxy Vale</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>sakura_tempest</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>roxy</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>art/fighters/roxy_main.webp</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n"/>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n"/>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n"/>
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n"/>
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
+      <c r="E48" s="7" t="n"/>
+      <c r="F48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n"/>
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n"/>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n"/>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n"/>
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n"/>
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
+      <c r="E54" s="7" t="n"/>
+      <c r="F54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n"/>
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="7" t="n"/>
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n"/>
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n"/>
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="7" t="n"/>
+      <c r="E57" s="7" t="n"/>
+      <c r="F57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n"/>
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
+      <c r="E58" s="7" t="n"/>
+      <c r="F58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n"/>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n"/>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n"/>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="7" t="n"/>
+      <c r="E61" s="7" t="n"/>
+      <c r="F61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n"/>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
+      <c r="E62" s="7" t="n"/>
+      <c r="F62" s="7" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n"/>
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="7" t="n"/>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dist/Foxy_Fight_Sheet_Template.xlsx
+++ b/dist/Foxy_Fight_Sheet_Template.xlsx
@@ -808,7 +808,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>CutIns: one row per fighter + move. fighter = a style id, an opponent id or a Fighters id. move = a card id, a tag (Opener, Light, Heavy, Finisher, Guard, Wild), Knockdown, Victory, or blank for any move. profile_0..2 / pov_0..2 = image paths or https:// links.</t>
+          <t>CutIns: one row per fighter + move. fighter = a style id, an opponent id or a Fighters id. move = a card id, a tag (Opener, Light, Heavy, Finisher, Guard, Wild), Knockdown, Victory, or blank for any move. profile_0..2 / pov_0..2 = image paths or https:// links. A path ending in .* (used for Victory) accepts any image type: the game uses the first of .png .jpg .jpeg .webp .gif .avif .svg it finds.</t>
         </is>
       </c>
     </row>
@@ -9977,32 +9977,32 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/cherry-bomb/victory_profile_0.png</t>
+          <t>art/cutins/cherry-bomb/victory_profile_0.*</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/cherry-bomb/victory_profile_1.png</t>
+          <t>art/cutins/cherry-bomb/victory_profile_1.*</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/cherry-bomb/victory_profile_2.png</t>
+          <t>art/cutins/cherry-bomb/victory_profile_2.*</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/cherry-bomb/victory_pov_0.png</t>
+          <t>art/cutins/cherry-bomb/victory_pov_0.*</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/cherry-bomb/victory_pov_1.png</t>
+          <t>art/cutins/cherry-bomb/victory_pov_1.*</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/cherry-bomb/victory_pov_2.png</t>
+          <t>art/cutins/cherry-bomb/victory_pov_2.*</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -10447,32 +10447,32 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/main-event/victory_profile_0.png</t>
+          <t>art/cutins/main-event/victory_profile_0.*</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/main-event/victory_profile_1.png</t>
+          <t>art/cutins/main-event/victory_profile_1.*</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/main-event/victory_profile_2.png</t>
+          <t>art/cutins/main-event/victory_profile_2.*</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/main-event/victory_pov_0.png</t>
+          <t>art/cutins/main-event/victory_pov_0.*</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/main-event/victory_pov_1.png</t>
+          <t>art/cutins/main-event/victory_pov_1.*</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/main-event/victory_pov_2.png</t>
+          <t>art/cutins/main-event/victory_pov_2.*</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -10823,32 +10823,32 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/velvet-hammer/victory_profile_0.png</t>
+          <t>art/cutins/velvet-hammer/victory_profile_0.*</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/velvet-hammer/victory_profile_1.png</t>
+          <t>art/cutins/velvet-hammer/victory_profile_1.*</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/velvet-hammer/victory_profile_2.png</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>art/cutins/velvet-hammer/victory_pov_0.png</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>art/cutins/velvet-hammer/victory_pov_1.png</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>art/cutins/velvet-hammer/victory_pov_2.png</t>
+          <t>art/cutins/velvet-hammer/victory_profile_2.*</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/victory_pov_0.*</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/victory_pov_1.*</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/velvet-hammer/victory_pov_2.*</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -11293,32 +11293,32 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/brick-house/victory_profile_0.png</t>
+          <t>art/cutins/brick-house/victory_profile_0.*</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/brick-house/victory_profile_1.png</t>
+          <t>art/cutins/brick-house/victory_profile_1.*</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/brick-house/victory_profile_2.png</t>
+          <t>art/cutins/brick-house/victory_profile_2.*</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/brick-house/victory_pov_0.png</t>
+          <t>art/cutins/brick-house/victory_pov_0.*</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/brick-house/victory_pov_1.png</t>
+          <t>art/cutins/brick-house/victory_pov_1.*</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/brick-house/victory_pov_2.png</t>
+          <t>art/cutins/brick-house/victory_pov_2.*</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -11553,17 +11553,17 @@
       <c r="E44" s="5" t="inlineStr"/>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/lola-lux/victory_pov_0.png</t>
+          <t>art/cutins/lola-lux/victory_pov_0.*</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/lola-lux/victory_pov_1.png</t>
+          <t>art/cutins/lola-lux/victory_pov_1.*</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/lola-lux/victory_pov_2.png</t>
+          <t>art/cutins/lola-lux/victory_pov_2.*</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -11798,17 +11798,17 @@
       <c r="E51" s="5" t="inlineStr"/>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/dolores-dee-maddox/victory_pov_0.png</t>
+          <t>art/cutins/dolores-dee-maddox/victory_pov_0.*</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/dolores-dee-maddox/victory_pov_1.png</t>
+          <t>art/cutins/dolores-dee-maddox/victory_pov_1.*</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/dolores-dee-maddox/victory_pov_2.png</t>
+          <t>art/cutins/dolores-dee-maddox/victory_pov_2.*</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -12043,17 +12043,17 @@
       <c r="E58" s="5" t="inlineStr"/>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/vicki-high-score-starr/victory_pov_0.png</t>
+          <t>art/cutins/vicki-high-score-starr/victory_pov_0.*</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/vicki-high-score-starr/victory_pov_1.png</t>
+          <t>art/cutins/vicki-high-score-starr/victory_pov_1.*</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/vicki-high-score-starr/victory_pov_2.png</t>
+          <t>art/cutins/vicki-high-score-starr/victory_pov_2.*</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -12288,17 +12288,17 @@
       <c r="E65" s="5" t="inlineStr"/>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/ingrid-kessler/victory_pov_0.png</t>
+          <t>art/cutins/ingrid-kessler/victory_pov_0.*</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/ingrid-kessler/victory_pov_1.png</t>
+          <t>art/cutins/ingrid-kessler/victory_pov_1.*</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/ingrid-kessler/victory_pov_2.png</t>
+          <t>art/cutins/ingrid-kessler/victory_pov_2.*</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -12533,17 +12533,17 @@
       <c r="E72" s="5" t="inlineStr"/>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/scarlett-delacroix/victory_pov_0.png</t>
+          <t>art/cutins/scarlett-delacroix/victory_pov_0.*</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/scarlett-delacroix/victory_pov_1.png</t>
+          <t>art/cutins/scarlett-delacroix/victory_pov_1.*</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/scarlett-delacroix/victory_pov_2.png</t>
+          <t>art/cutins/scarlett-delacroix/victory_pov_2.*</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -12813,17 +12813,17 @@
       <c r="E80" s="5" t="inlineStr"/>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/madame-ruby/victory_pov_0.png</t>
+          <t>art/cutins/madame-ruby/victory_pov_0.*</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/madame-ruby/victory_pov_1.png</t>
+          <t>art/cutins/madame-ruby/victory_pov_1.*</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/madame-ruby/victory_pov_2.png</t>
+          <t>art/cutins/madame-ruby/victory_pov_2.*</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">

--- a/dist/Foxy_Fight_Sheet_Template.xlsx
+++ b/dist/Foxy_Fight_Sheet_Template.xlsx
@@ -777,7 +777,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>End-of-fight images: Opponents tab win_art (shown when you beat her) and loss_art (shown when she beats you). Config default_win_art / default_loss_art cover any blanks. Wide 16:9 images work best.</t>
+          <t>End-of-fight images: Opponents tab win_art (shown when you beat her) and loss_art (shown when she beats you). Config default_win_art / default_loss_art cover any blanks. Any shape works; the whole picture is shown.</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>CutIns: one row per fighter + move. fighter = a style id, an opponent id or a Fighters id. move = a card id, a tag (Opener, Light, Heavy, Finisher, Guard, Wild), Knockdown, Victory, or blank for any move. profile_0..2 / pov_0..2 = image paths or https:// links. A path ending in .* (used for Victory) accepts any image type: the game uses the first of .png .jpg .jpeg .webp .gif .avif .svg it finds.</t>
+          <t>CutIns: one row per fighter + move. fighter = a style id, an opponent id or a Fighters id. move = a card id, a tag (Opener, Light, Heavy, Finisher, Guard, Wild), Knockdown, Victory, or blank for any move. profile_0..2 / pov_0..2 = image paths or https:// links. A path ending in .* (used for Victory and the T.K.O. POV, Knockdown pov_2) accepts any image type: the game uses the first of .png .jpg .jpeg .webp .gif .avif .svg it finds.</t>
         </is>
       </c>
     </row>
@@ -9953,9 +9953,9 @@
           <t>art/cutins/cherry-bomb/knockdown_pov_1.png</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>art/cutins/cherry-bomb/knockdown_pov_2.png</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/cherry-bomb/knockdown_pov_2.*</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -10423,9 +10423,9 @@
           <t>art/cutins/main-event/knockdown_pov_1.png</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>art/cutins/main-event/knockdown_pov_2.png</t>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/main-event/knockdown_pov_2.*</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/velvet-hammer/knockdown_pov_2.png</t>
+          <t>art/cutins/velvet-hammer/knockdown_pov_2.*</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -11269,9 +11269,9 @@
           <t>art/cutins/brick-house/knockdown_pov_1.png</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>art/cutins/brick-house/knockdown_pov_2.png</t>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/brick-house/knockdown_pov_2.*</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>art/cutins/lola-lux/knockdown_pov_2.png</t>
+          <t>art/cutins/lola-lux/knockdown_pov_2.*</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/dolores-dee-maddox/knockdown_pov_2.png</t>
+          <t>art/cutins/dolores-dee-maddox/knockdown_pov_2.*</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/vicki-high-score-starr/knockdown_pov_2.png</t>
+          <t>art/cutins/vicki-high-score-starr/knockdown_pov_2.*</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/ingrid-kessler/knockdown_pov_2.png</t>
+          <t>art/cutins/ingrid-kessler/knockdown_pov_2.*</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>art/cutins/scarlett-delacroix/knockdown_pov_2.png</t>
+          <t>art/cutins/scarlett-delacroix/knockdown_pov_2.*</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
@@ -12786,9 +12786,9 @@
           <t>art/cutins/madame-ruby/knockdown_pov_1.png</t>
         </is>
       </c>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t>art/cutins/madame-ruby/knockdown_pov_2.png</t>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>art/cutins/madame-ruby/knockdown_pov_2.*</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">

--- a/dist/Foxy_Fight_Sheet_Template.xlsx
+++ b/dist/Foxy_Fight_Sheet_Template.xlsx
@@ -851,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1493,17 +1493,17 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>pvp_turn_seconds</t>
+          <t>tko_cutin_seconds</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Versus: seconds per turn before it ends automatically. 0 = no clock</t>
+          <t>Seconds the T.K.O. cut-in you land (Knockdown pov_2) stays up before the result screen. Click or press a key to skip. The T.K.O. you take stays about 2.5 seconds</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1515,17 +1515,17 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>pvp_disconnect_seconds</t>
+          <t>pvp_turn_seconds</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Versus: how long to wait for a dropped player before the other wins by forfeit</t>
+          <t>Versus: seconds per turn before it ends automatically. 0 = no clock</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1537,17 +1537,17 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>pvp_xp_win</t>
+          <t>pvp_disconnect_seconds</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Versus: XP for a win, added to the character you fought with</t>
+          <t>Versus: how long to wait for a dropped player before the other wins by forfeit</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1559,30 +1559,46 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>pvp_xp_win</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Versus: XP for a win, added to the character you fought with</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
           <t>pvp_xp_loss</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Versus: XP for a loss</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Claude</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n"/>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
@@ -1931,6 +1947,12 @@
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n"/>
+      <c r="B93" s="7" t="n"/>
+      <c r="C93" s="7" t="n"/>
+      <c r="D93" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
